--- a/DOSSIES_MULTIFORMATO/FHAJ/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FHAJ/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE01910</t>
+          <t>2020NE01911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>249.22</v>
+        <v>1.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE00004/2020, conforme Decreto nº 43.042/2020 - Encerramento da execução orçamentária, financeira e contábil do exercício de 2020.</t>
+          <t>Anulação do saldo da NE00819/2020, conforme Decreto nº 43.042/2020 - Encerramento da execução orçamentária, financeira e contábil do exercício de 2020.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE01911</t>
+          <t>2020NE01910</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.83</v>
+        <v>249.22</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE00819/2020, conforme Decreto nº 43.042/2020 - Encerramento da execução orçamentária, financeira e contábil do exercício de 2020.</t>
+          <t>Anulação do saldo da NE00004/2020, conforme Decreto nº 43.042/2020 - Encerramento da execução orçamentária, financeira e contábil do exercício de 2020.</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2017NE00275</t>
+          <t>2017NE00274</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indenizações, Parecer Jurídico nº 40/2017-ASJUR/FHAJ, Termo de Ajuste de Contas nº 14/2017-FHAJ, referente a prestação de serviço de acesso gerenciado a rede mundial - por Mbps (de 1até 10 Mbps) - (5,</t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 39/2017-FHAJ, Termo de Ajuste de Contas nº 13/2017-FHAJ, referente a prestação de serviço de acesso gerenciado a rede mundial - por Mbps (de 1até 10 Mbps) - (5,000 x </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2017NE00274</t>
+          <t>2017NE00275</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -801,14 +801,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 39/2017-FHAJ, Termo de Ajuste de Contas nº 13/2017-FHAJ, referente a prestação de serviço de acesso gerenciado a rede mundial - por Mbps (de 1até 10 Mbps) - (5,000 x </t>
+          <t>Indenizações, Parecer Jurídico nº 40/2017-ASJUR/FHAJ, Termo de Ajuste de Contas nº 14/2017-FHAJ, referente a prestação de serviço de acesso gerenciado a rede mundial - por Mbps (de 1até 10 Mbps) - (5,</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE01311</t>
+          <t>2016NE01325</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.72</v>
+        <v>11.57</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -827,14 +827,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 075/2016 PARA AJUSTE ORÇAMENTÁRIO, CONF. ORIENTAÇÃO SEFAZ-AM.</t>
+          <t>Anulação do saldo da NE 200/2016 em atendimento ao Aviso n. 02/2017 e Comunicação nr. 13 de 15/12/2016 - SEFAZ-AM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE01325</t>
+          <t>2016NE01311</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.57</v>
+        <v>1.72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE 200/2016 em atendimento ao Aviso n. 02/2017 e Comunicação nr. 13 de 15/12/2016 - SEFAZ-AM</t>
+          <t>ANULAÇÃO PARCIAL DA NE 075/2016 PARA AJUSTE ORÇAMENTÁRIO, CONF. ORIENTAÇÃO SEFAZ-AM.</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025NE0000385</t>
+          <t>2025NE0000386</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -913,19 +913,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000386</t>
+          <t>2025NE0000385</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023NE0001622</t>
+          <t>2023NE0001677</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2225.17</v>
+        <v>8111.66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO DE EMPENHO , EM VIRTUDE DO ENCERRAMENTO DO EXECÍCIO, CONFORME DECRETO Nº 48.363/2023 DE 27/10/2023.</t>
+          <t>ANULAÇÃO DE SALDO DE EMPENHO , EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 48.363/2023 DE 27/10/2023.</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023NE0001677</t>
+          <t>2023NE0001622</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8111.66</v>
+        <v>2225.17</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO DE EMPENHO , EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 48.363/2023 DE 27/10/2023.</t>
+          <t>ANULAÇÃO DE SALDO DE EMPENHO , EM VIRTUDE DO ENCERRAMENTO DO EXECÍCIO, CONFORME DECRETO Nº 48.363/2023 DE 27/10/2023.</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023NE0000761</t>
+          <t>2023NE0000760</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8420.200000000001</v>
+        <v>2297.09</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1223,19 +1223,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023NE0000760</t>
+          <t>2023NE0000761</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2297.09</v>
+        <v>8420.200000000001</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1253,14 +1253,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE01512</t>
+          <t>2018NE01496</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49.18</v>
+        <v>0.02</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE00063/2018, conforme orientação da Gerência de Inspetoria da Sefaz, para o encerramento do exercício financeiro de 2018.</t>
+          <t>Anulação do saldo da NE00182/2018, conforme orientação da Gerência de Inspetoria da Sefaz, para o encerramento do exercício financeiro de 2018.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE01496</t>
+          <t>2018NE01512</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.02</v>
+        <v>49.18</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE00182/2018, conforme orientação da Gerência de Inspetoria da Sefaz, para o encerramento do exercício financeiro de 2018.</t>
+          <t>Anulação do saldo da NE00063/2018, conforme orientação da Gerência de Inspetoria da Sefaz, para o encerramento do exercício financeiro de 2018.</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2023NE0000756</t>
+          <t>2023NE0000757</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2297.09</v>
+        <v>8111.66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2023NE0000757</t>
+          <t>2023NE0000756</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8111.66</v>
+        <v>2297.09</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026NE0000115</t>
+          <t>2026NE0000114</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026NE0000114</t>
+          <t>2026NE0000115</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1582,12 +1582,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2021NE0001757</t>
+          <t>2021NE0001760</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7457.56</v>
+        <v>1979.55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1605,19 +1605,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: novembro/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: novembro/2021.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2021NE0001760</t>
+          <t>2021NE0001757</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1979.55</v>
+        <v>7457.56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1635,19 +1635,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: novembro/2021.</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: novembro/2021.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2023NE0001349</t>
+          <t>2023NE0001350</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8420.200000000001</v>
+        <v>2297.09</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1665,19 +1665,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2023NE0001350</t>
+          <t>2023NE0001349</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2297.09</v>
+        <v>8420.200000000001</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1695,28 +1695,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018NE00739</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2018NE00738</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>26/07/2018</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1666.67</v>
+        <v>1133.35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1725,24 +1721,28 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1. Termo Aditivo ao Contrato 09/2017 - Internet banda larga - Março/2018</t>
+          <t>Contrato 09/2017 - 01 a 05/03/2018 Internet Banda Larga</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2018NE00738</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>2018NE00739</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>26/07/2018</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1133.35</v>
+        <v>1666.67</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Contrato 09/2017 - 01 a 05/03/2018 Internet Banda Larga</t>
+          <t>1. Termo Aditivo ao Contrato 09/2017 - Internet banda larga - Março/2018</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026NE0000104</t>
+          <t>2026NE0000110</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1867,19 +1867,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026NE0000109</t>
+          <t>2026NE0000105</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1897,14 +1897,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026NE0000107</t>
+          <t>2026NE0000111</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026NE0000108</t>
+          <t>2026NE0000106</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2717.66</v>
+        <v>9256</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1957,19 +1957,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026NE0000106</t>
+          <t>2026NE0000108</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9256</v>
+        <v>2717.66</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1987,14 +1987,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026NE0000111</t>
+          <t>2026NE0000107</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2024,12 +2024,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026NE0000105</t>
+          <t>2026NE0000109</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2047,19 +2047,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026NE0000110</t>
+          <t>2026NE0000104</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025NE0001068</t>
+          <t>2025NE0001069</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2717.66</v>
+        <v>1261.99</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025NE0001069</t>
+          <t>2025NE0001068</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1261.99</v>
+        <v>2717.66</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2234,12 +2234,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2021NE0000738</t>
+          <t>2021NE0000737</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3356.88</v>
+        <v>14915.52</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,19 +2257,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: maio e junho/2021 (parcial).</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: maio e junho/2021.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2021NE0000737</t>
+          <t>2021NE0000738</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14915.52</v>
+        <v>3356.88</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: maio e junho/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: maio e junho/2021 (parcial).</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024NE0001758</t>
+          <t>2024NE0001756</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2406,19 +2406,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>referente à Nota Fiscal nº 47528, de 12.08.2024, no valor total de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso d</t>
+          <t>referente à Nota Fiscal nº 47526, de 12.08.2024, no valor total de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024NE0001766</t>
+          <t>2024NE0001757</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9256.1</v>
+        <v>2297.09</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2436,19 +2436,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>referente à Nota Fiscal nº 47527, de 12.08.2024, no valor de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso de Sist</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024NE0001757</t>
+          <t>2024NE0001766</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2297.09</v>
+        <v>9256.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2466,14 +2466,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>referente à Nota Fiscal nº 47527, de 12.08.2024, no valor de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso de Sist</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024NE0001756</t>
+          <t>2024NE0001758</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2496,19 +2496,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>referente à Nota Fiscal nº 47526, de 12.08.2024, no valor total de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso d</t>
+          <t>referente à Nota Fiscal nº 47528, de 12.08.2024, no valor total de R$ 2.297,09 (dois mil, duzentos e noventa e sete reais e nove centavos), em consequência da prestação de serviços de Licença de Uso d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2023NE0001096</t>
+          <t>2023NE0001095</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2297.09</v>
+        <v>8420.200000000001</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2526,19 +2526,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2023NE0001095</t>
+          <t>2023NE0001096</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8420.200000000001</v>
+        <v>2297.09</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2556,19 +2556,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t xml:space="preserve">Contratação de empresa especializada nos serviços de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB, para publicação de inf., noticias, videos e imagens via WEBSITE </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0001234</t>
+          <t>2022NE0001235</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2157.7</v>
+        <v>7525.43</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: junho/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: junho/2022.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2022NE0001235</t>
+          <t>2022NE0001234</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7525.43</v>
+        <v>2157.7</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2616,19 +2616,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: junho/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: junho/2022.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025NE0000463</t>
+          <t>2025NE0000462</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2646,19 +2646,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025NE0000462</t>
+          <t>2025NE0000463</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2022NE0001892</t>
+          <t>2022NE0001891</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2157.7</v>
+        <v>7525.43</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2796,19 +2796,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Setembro/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Setembro/2022.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2022NE0001891</t>
+          <t>2022NE0001892</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7525.43</v>
+        <v>2157.7</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Setembro/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Setembro/2022.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2016NE00860</t>
+          <t>2016NE00858</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2856,14 +2856,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 219/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t>Indenizações, Parecer Jurídico nº 217/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00, competência: 0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2016NE00862</t>
+          <t>2016NE00861</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2886,14 +2886,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 221/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 220/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2016NE00860</t>
+          <t>2016NE00859</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2916,14 +2916,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 219/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 218/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2016NE00862</t>
+          <t>2016NE00861</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 221/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 220/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2016NE00858</t>
+          <t>2016NE00859</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Indenizações, Parecer Jurídico nº 217/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00, competência: 0</t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 218/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2016NE00859</t>
+          <t>2016NE00858</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3006,14 +3006,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 218/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t>Indenizações, Parecer Jurídico nº 217/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00, competência: 0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2016NE00861</t>
+          <t>2016NE00862</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3036,14 +3036,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 220/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 221/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2016NE00859</t>
+          <t>2016NE00860</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3066,14 +3066,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 218/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 219/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2016NE00861</t>
+          <t>2016NE00862</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 220/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 221/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2016NE00858</t>
+          <t>2016NE00860</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3126,19 +3126,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Indenizações, Parecer Jurídico nº 217/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00, competência: 0</t>
+          <t xml:space="preserve">Indenizações, Parecer Jurídico nº 219/2016-ASJUR/FHAJ, referente a prestação de serviços de acesso gerenciado a Rede Mundial por Mbps (de 1 até 10 Mbps) - (5,000 x 680,00 = R$ 3.400,00), competência: </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020NE00985</t>
+          <t>2020NE00984</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1678.44</v>
+        <v>15100.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3156,19 +3156,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: julho/2020.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Junho e Julho/2020.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020NE00984</t>
+          <t>2020NE00985</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>15100.2</v>
+        <v>1678.44</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Junho e Julho/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: julho/2020.</t>
         </is>
       </c>
     </row>
@@ -3223,10 +3223,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2021NE0000025</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>2021NE0000021</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>20/01/2021</t>
@@ -3242,7 +3246,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 21/2021 POR DATA INCORRETA.</t>
+          <t>3º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 10 Mbps. Período: jan, fev e de 01 a 05 de mar</t>
         </is>
       </c>
     </row>
@@ -3279,14 +3283,10 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2021NE0000021</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2021NE0000025</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>20/01/2021</t>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 10 Mbps. Período: jan, fev e de 01 a 05 de mar</t>
+          <t>ANULAÇÃO DA NE 21/2021 POR DATA INCORRETA.</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2022NE0000905</t>
+          <t>2022NE0000904</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2157.7</v>
+        <v>7525.43</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3362,19 +3362,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Maio/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado; Período: Maio/2022.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2022NE0000904</t>
+          <t>2022NE0000905</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7525.43</v>
+        <v>2157.7</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3392,17 +3392,21 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado; Período: Maio/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Maio/2022.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2021NE0000004</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>2021NE0000001</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>19/01/2021</t>
@@ -3418,21 +3422,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 1/2021 POR DATA INCORRETA.</t>
+          <t>3º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 10 Mbps. Período: jan, fev e de 01 a 05 de mar</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2021NE0000001</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2021NE0000004</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>19/01/2021</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 10 Mbps. Período: jan, fev e de 01 a 05 de mar</t>
+          <t>ANULAÇÃO DA NE 1/2021 POR DATA INCORRETA.</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2022NE0002056</t>
+          <t>2022NE0002057</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7525.43</v>
+        <v>2157.7</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3504,19 +3504,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Outubro/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Outubro/2022.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2022NE0002057</t>
+          <t>2022NE0002056</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2157.7</v>
+        <v>7525.43</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Outubro/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Outubro/2022.</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2022NE0000224</t>
+          <t>2022NE0000226</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2022NE0000226</t>
+          <t>2022NE0000224</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3658,12 +3658,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2021NE0001070</t>
+          <t>2021NE0001068</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1678.44</v>
+        <v>7457.56</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3681,19 +3681,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Agosto/2021 (parcial).</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Agosto/2021.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2021NE0001068</t>
+          <t>2021NE0001070</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7457.56</v>
+        <v>1678.44</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Agosto/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Agosto/2021 (parcial).</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2015NE00199</t>
+          <t>2015NE00209</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5279</v>
+        <v>9390.08</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3831,19 +3831,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>COBERTURA MARÇO 2015</t>
+          <t>Cobertura março 2015</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2015NE00209</t>
+          <t>2015NE00199</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9390.08</v>
+        <v>5279</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3861,19 +3861,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cobertura março 2015</t>
+          <t>COBERTURA MARÇO 2015</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025NE0001212</t>
+          <t>2025NE0001197</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2297.09</v>
+        <v>2717.66</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3891,19 +3891,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e i</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025NE0001206</t>
+          <t>2025NE0001195</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025NE0001218</t>
+          <t>2025NE0001216</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>835.9</v>
+        <v>9256.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3958,66 +3958,65 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025NE0001209</t>
+          <t>2025NE0001215</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>8/2022</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>9256.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F115">
+        <f> Referente a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado, com velocidade de 37 Mbps, pelo período de 12 (doze) meses, par</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025NE0001210</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>1/2018</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>15/10/2025</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D116" t="n">
         <v>2297.09</v>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="F115">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F116">
         <f> Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e</f>
         <v/>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2025NE0001217</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>8/2022</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>9256.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Referente ao 1º Termo Aditivo ao Contrato nº 008/2022-FHAJ, cujo o objeto é a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado,</t>
-        </is>
-      </c>
-    </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025NE0001208</t>
+          <t>2025NE0001211</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4031,22 +4030,23 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2220.52</v>
+        <v>2297.09</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
-      <c r="F117">
-        <f> Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e</f>
-        <v/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e i</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025NE0001205</t>
+          <t>2025NE0001219</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4067,16 +4067,15 @@
           <t>Ativo</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
-        </is>
+      <c r="F118">
+        <f> Referente a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado, com velocidade de 37 Mbps, pelo período de 12 (doze) meses, par</f>
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025NE0001214</t>
+          <t>2025NE0001213</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4105,12 +4104,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025NE0001196</t>
+          <t>2025NE0001207</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4119,7 +4118,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4128,19 +4127,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025NE0001207</t>
+          <t>2025NE0001196</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4149,7 +4148,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4158,14 +4157,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025NE0001213</t>
+          <t>2025NE0001214</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4194,7 +4193,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025NE0001219</t>
+          <t>2025NE0001205</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4215,15 +4214,16 @@
           <t>Ativo</t>
         </is>
       </c>
-      <c r="F123">
-        <f> Referente a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado, com velocidade de 37 Mbps, pelo período de 12 (doze) meses, par</f>
-        <v/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025NE0001211</t>
+          <t>2025NE0001208</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4237,81 +4237,81 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2297.09</v>
+        <v>2220.52</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e i</t>
-        </is>
+      <c r="F124">
+        <f> Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e</f>
+        <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0001210</t>
+          <t>2025NE0001217</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
+          <t>8/2022</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>9256.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Referente ao 1º Termo Aditivo ao Contrato nº 008/2022-FHAJ, cujo o objeto é a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado,</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025NE0001209</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>1/2018</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>15/10/2025</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D126" t="n">
         <v>2297.09</v>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="F125">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F126">
         <f> Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e</f>
         <v/>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2025NE0001215</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>8/2022</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>9256.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="F126">
-        <f> Referente a contratação de pessoa jurídica especializada para prestação de serviços de acesso à Internet Banda Larga, com IP dedicado, com velocidade de 37 Mbps, pelo período de 12 (doze) meses, par</f>
-        <v/>
-      </c>
-    </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025NE0001216</t>
+          <t>2025NE0001218</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>9256.1</v>
+        <v>835.9</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4341,12 +4341,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025NE0001195</t>
+          <t>2025NE0001206</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4364,19 +4364,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025NE0001197</t>
+          <t>2025NE0001212</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2717.66</v>
+        <v>2297.09</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4394,14 +4394,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Referente a contratação de de pessoa jurídica especializada em serviços de informática, compreendendo à disponibilização de gestor de conteúdo WEB, para publicação de informações, notícias, vídeos e i</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020NE00730</t>
+          <t>2020NE00729</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7550.1</v>
+        <v>91.2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4424,14 +4424,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: maio/2020.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Abril/2020 (diferença).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020NE00729</t>
+          <t>2020NE00730</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>91.2</v>
+        <v>7550.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4454,21 +4454,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Abril/2020 (diferença).</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: maio/2020.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2016NE01142</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>P.144/2016</t>
-        </is>
-      </c>
+          <t>2016NE01141</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>14/12/2016</t>
@@ -4484,17 +4480,21 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0440/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19574, emitida em, 12/08/2016, competência 11/2015. Parecer jurídico 241/2016- A</t>
+          <t>CANCELAMENTO DA NE 1123/2016 PELO MOTIVO DO NR. DO PROCESSO INCORRETO.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2016NE01141</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>2016NE01142</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>P.144/2016</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
           <t>14/12/2016</t>
@@ -4510,19 +4510,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE 1123/2016 PELO MOTIVO DO NR. DO PROCESSO INCORRETO.</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0440/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19574, emitida em, 12/08/2016, competência 11/2015. Parecer jurídico 241/2016- A</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2021NE0000871</t>
+          <t>2021NE0000872</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1678.44</v>
+        <v>7457.56</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4540,19 +4540,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Julho/2021 (parcial).</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Julho/2021.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2021NE0000872</t>
+          <t>2021NE0000871</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7457.56</v>
+        <v>1678.44</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Julho/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Julho/2021 (parcial).</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020NE01532</t>
+          <t>2020NE01531</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Dezembro/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Novembro/2020.</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020NE01531</t>
+          <t>2020NE01532</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4716,19 +4716,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Novembro/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Dezembro/2020.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020NE01388</t>
+          <t>2020NE01387</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7550.1</v>
+        <v>1678.44</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4746,19 +4746,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Outubro/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Outubro/2020.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2020NE01387</t>
+          <t>2020NE01388</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1678.44</v>
+        <v>7550.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4776,19 +4776,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Outubro/2020.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Outubro/2020.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026NE0000189</t>
+          <t>2026NE0000190</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>9256</v>
+        <v>2717.66</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026NE0000190</t>
+          <t>2026NE0000189</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2717.66</v>
+        <v>9256</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
@@ -4933,12 +4933,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2022NE0002375</t>
+          <t>2022NE0002368</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15050.86</v>
+        <v>4315.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4956,19 +4956,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Novembro e dezembro/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Novembro e dezembro/2022.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2022NE0002368</t>
+          <t>2022NE0002375</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4315.4</v>
+        <v>15050.86</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4986,14 +4986,14 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Novembro e dezembro/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Novembro e dezembro/2022.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2016NE01122</t>
+          <t>2016NE01121</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0439/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19573, emitida em, 12/08/2016, competência 10/2015. Parecer jurídico 240/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0438/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19572, emitida em, 12/08/2016, competência 09/2015. Parecer jurídico 239/2016- A</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2016NE01119</t>
+          <t>2016NE01120</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0436/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19570, emitida em, 12/08/2016, competência 07/2015. Parecer jurídico 237/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0437/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19571, emitida em, 12/08/2016, competência 08/2015. Parecer jurídico 238/2016- A</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2016NE01124</t>
+          <t>2016NE01123</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0441/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19575, emitida em, 12/08/2016, competência 12/2015. Parecer jurídico 242/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0440/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19574, emitida em, 12/08/2016, competência 11/2015. Parecer jurídico 241/2016- A</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2016NE01123</t>
+          <t>2016NE01124</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0440/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19574, emitida em, 12/08/2016, competência 11/2015. Parecer jurídico 241/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0441/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19575, emitida em, 12/08/2016, competência 12/2015. Parecer jurídico 242/2016- A</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2016NE01120</t>
+          <t>2016NE01119</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0437/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19571, emitida em, 12/08/2016, competência 08/2015. Parecer jurídico 238/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0436/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19570, emitida em, 12/08/2016, competência 07/2015. Parecer jurídico 237/2016- A</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2016NE01121</t>
+          <t>2016NE01122</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores, conforme RD 0438/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19572, emitida em, 12/08/2016, competência 09/2015. Parecer jurídico 239/2016- A</t>
+          <t>Despesas De Exercícios Anteriores, conforme RD 0439/2016, referente a serviço de acesso à Rede Mundial -Internet, NFS-e 19573, emitida em, 12/08/2016, competência 10/2015. Parecer jurídico 240/2016- A</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2020NE01509</t>
+          <t>2020NE01510</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - ago/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - jul/2019.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020NE01510</t>
+          <t>2020NE01509</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - jul/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - ago/2019.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2022NE0001434</t>
+          <t>2022NE0001433</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>15050.86</v>
+        <v>4315.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: julho e agosto/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: julho e agosto/2022.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2022NE0001433</t>
+          <t>2022NE0001434</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4315.4</v>
+        <v>15050.86</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: julho e agosto/2022.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: julho e agosto/2022.</t>
         </is>
       </c>
     </row>
@@ -5431,21 +5431,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2020NE00438</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2020NE00434</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>11/03/2020</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6291.75</v>
+        <v>6215.75</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5454,24 +5450,28 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: 06 a 31/03/2020.</t>
+          <t>Anulação parcial da NE00004/2020, pelo motivo do valor total incorreto.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2020NE00434</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>2020NE00438</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr">
         <is>
           <t>11/03/2020</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6215.75</v>
+        <v>6291.75</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE00004/2020, pelo motivo do valor total incorreto.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: 06 a 31/03/2020.</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2020NE01508</t>
+          <t>2020NE01502</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7458.9</v>
+        <v>1623.56</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - set/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - nov/2019.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2020NE01507</t>
+          <t>2020NE01501</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7458.9</v>
+        <v>1623.56</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5562,14 +5562,14 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - out/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - dez/2019.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2020NE01506</t>
+          <t>2020NE01504</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>7458.9</v>
+        <v>1623.56</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - nov/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - ago/2019.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2020NE01503</t>
+          <t>2020NE01505</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1623.56</v>
+        <v>7458.9</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5614,14 +5614,14 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - out/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - dez/2019.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2020NE01505</t>
+          <t>2020NE01503</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7458.9</v>
+        <v>1623.56</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5640,14 +5640,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - dez/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - out/2019.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020NE01504</t>
+          <t>2020NE01506</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1623.56</v>
+        <v>7458.9</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5666,14 +5666,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - ago/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - nov/2019.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2020NE01501</t>
+          <t>2020NE01507</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1623.56</v>
+        <v>7458.9</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5692,14 +5692,14 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - dez/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - out/2019.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2020NE01502</t>
+          <t>2020NE01508</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1623.56</v>
+        <v>7458.9</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>DEAS, serviços de banda larga - internet - nov/2019.</t>
+          <t>DEAS, serviços de banda larga - internet - set/2019.</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021NE0000369</t>
+          <t>2021NE0000368</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7457.76</v>
+        <v>5035.32</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5808,19 +5808,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Abril/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Fevereiro a abril/2021.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021NE0000368</t>
+          <t>2021NE0000369</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5035.32</v>
+        <v>7457.76</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Fevereiro a abril/2021.</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: Abril/2021.</t>
         </is>
       </c>
     </row>
@@ -5905,12 +5905,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021NE0001589</t>
+          <t>2021NE0001590</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>7457.56</v>
+        <v>1678.44</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5928,19 +5928,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: outubro/2021.</t>
+          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: outubro/2021 (parcial).</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021NE0001590</t>
+          <t>2021NE0001589</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1678.44</v>
+        <v>7457.56</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>3º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: outubro/2021 (parcial).</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: outubro/2021.</t>
         </is>
       </c>
     </row>
@@ -5995,12 +5995,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2017NE00499</t>
+          <t>2017NE00500</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>797.62</v>
+        <v>2040</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6018,19 +6018,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Referente ao 5º Termo Aditivo ao Contrato nº 004/2012-FHAJ, serv. de implantação do sistema SIGS- Sistema Inteligente de Controle de Senhas.</t>
+          <t>Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, prestação de serv. de desenvolvimento, confecção e implantação de de páginas eletrônicas e hospedagem de site institucional.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2017NE00500</t>
+          <t>2017NE00499</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2040</v>
+        <v>797.62</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, prestação de serv. de desenvolvimento, confecção e implantação de de páginas eletrônicas e hospedagem de site institucional.</t>
+          <t>Referente ao 5º Termo Aditivo ao Contrato nº 004/2012-FHAJ, serv. de implantação do sistema SIGS- Sistema Inteligente de Controle de Senhas.</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2015NE00436</t>
+          <t>2015NE00350</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>374.17</v>
+        <v>5279</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6108,19 +6108,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>cobertura maio 2015</t>
+          <t>Reforço a NE00035/2015, 3º Termo Aditivo ao Contrato nº 011/2011-FHAJ, serviços eventuais de informática.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2015NE00376</t>
+          <t>2015NE00353</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>9390.08</v>
+        <v>398.81</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Reforço a NE00034/2015, 4º Termo Aditivo ao Contrato nº 12/2010-FHAJ, referente a serviços de acesso a Internet.</t>
+          <t>Reforço a NE00093/2015, 3º Termo Aditivo ao Contrato nº 004/2012-FHAJ, serviços serviço de implantação de software.</t>
         </is>
       </c>
     </row>
@@ -6175,12 +6175,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2015NE00353</t>
+          <t>2015NE00376</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>398.81</v>
+        <v>9390.08</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6198,19 +6198,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Reforço a NE00093/2015, 3º Termo Aditivo ao Contrato nº 004/2012-FHAJ, serviços serviço de implantação de software.</t>
+          <t>Reforço a NE00034/2015, 4º Termo Aditivo ao Contrato nº 12/2010-FHAJ, referente a serviços de acesso a Internet.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2015NE00350</t>
+          <t>2015NE00436</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5279</v>
+        <v>374.17</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Reforço a NE00035/2015, 3º Termo Aditivo ao Contrato nº 011/2011-FHAJ, serviços eventuais de informática.</t>
+          <t>cobertura maio 2015</t>
         </is>
       </c>
     </row>
@@ -6291,12 +6291,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2016NE01107</t>
+          <t>2016NE01093</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3081.37</v>
+        <v>398.81</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6314,14 +6314,14 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Despesas De Exercicios Anteriores, RD00276/16, SC00432/16, Referente a prestação de serviços de manutenção corretiva e preventiva em equipamentos de automação de escritório no período de outubro/14, C</t>
+          <t>Despesas De Exercícios Anteriores - RD 133/2016 - NFS 15096, de 09/07/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Julho/2015.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2016NE01098</t>
+          <t>2016NE01097</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6344,19 +6344,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 181/2016 - NFS 15160, de 15/07/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Junho/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 180/2016 - NFS 15161, de 15/07/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Julho/2015.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2016NE01095</t>
+          <t>2016NE01101</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1020.49</v>
+        <v>9895.27</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6374,19 +6374,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 178/2016 - NFS 15799, de 15/09/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Setembro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 257/2016 - NFS 12878, de 11/12/2014 - Ref. Contrato 12/2010, Serviço de acesso a internet -Banda Larga, competência Dezembro/2014.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2016NE01105</t>
+          <t>2016NE01089</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>5175.24</v>
+        <v>398.81</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6404,19 +6404,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Despesas De Exercicios Anteriores, RD00278/16, SC420/16, referente a prestação de serviço de manutenção corretiva e preventiva em equipamentos de automação de escritório no período de novembro/2014, C</t>
+          <t>Despesas De Exercícios Anteriores - RD 110/2016 - NFS 16509, de 10/11/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Novembro/2015.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2016NE01096</t>
+          <t>2016NE01094</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1020.49</v>
+        <v>398.81</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6434,19 +6434,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 179/2016 - NFS 15335, de 13/08/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Agosto/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 134/2016 - NFS 14807, de 12/06/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Junho/2015.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2016NE01109</t>
+          <t>2016NE01111</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>398.81</v>
+        <v>6429.09</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6464,19 +6464,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Despesas De Exercicios Anteriores, RD00117/16, SC00431/16, referente a prestação de serviços de manut. de sistemas de informatica desenvolvido por terceiros - manutenção mensal do sistema SICS - Siste</t>
+          <t>Referente ao 5º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de informática para confecção de páginas eletrônicas.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2016NE01081</t>
+          <t>2016NE01106</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>9895.27</v>
+        <v>2392.86</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6494,19 +6494,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 99/2016 - NFS 14497, de 12/05/2017 - Ref. Contrato 12/2010, Serviço de acesso a rede de internet, competência Maio/2015</t>
+          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2016NE01103</t>
+          <t>2016NE01084</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2035.16</v>
+        <v>1020.49</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6524,19 +6524,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 260/2016 - NFS 12236, de 20/10/2014 - Ref. Contrato 11/2011, Serviço de assistência técnica em software.</t>
+          <t>Despesas De Exercícios Anteriores - RD 105/2016 - NFS 16208, de 13/10/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Outubro/2015.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2016NE01104</t>
+          <t>2016NE01108</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5232.92</v>
+        <v>986.48</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6554,14 +6554,14 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 277/2016 - NFS 12881, de 11/12/2014 - Ref. Contrato 11/2011, Serviço eventuais de informática, competência Dezembro/2014.</t>
+          <t>Reforço - Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de informática para confecção de páginas eletrônicas.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2016NE01086</t>
+          <t>2016NE01083</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1020.49</v>
+        <v>306.15</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6584,14 +6584,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 107/2016 - NFS 17305, de 19/01/2016 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Dezembro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 100/2016 - NFS 16508, de 10/11/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Novembro/2015</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2016NE01099</t>
+          <t>2016NE01091</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6614,19 +6614,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 182/2016 - NFS 16837, de 02/12/2015 - Ref. Contrato 04/2012, Serviço de manutenção do Sistema SICS, competência Dezembro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 115/2016 - NFS 16209, de 13/10/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Outubro/2015.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2016NE01102</t>
+          <t>2016NE01090</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>9895.27</v>
+        <v>398.81</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 258/2016 - NFS 12100, de 13/10/2014 - Ref. Contrato 12/2010, Serviço de acesso a internet -Banda Larga, competência Outubro/2014.</t>
+          <t>Despesas De Exercícios Anteriores - RD 111/2016 - NFS 15800, de 15/09/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Setembro/2015.</t>
         </is>
       </c>
     </row>
@@ -6681,12 +6681,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2016NE01090</t>
+          <t>2016NE01102</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>398.81</v>
+        <v>9895.27</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 111/2016 - NFS 15800, de 15/09/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Setembro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 258/2016 - NFS 12100, de 13/10/2014 - Ref. Contrato 12/2010, Serviço de acesso a internet -Banda Larga, competência Outubro/2014.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2016NE01091</t>
+          <t>2016NE01099</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6734,14 +6734,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 115/2016 - NFS 16209, de 13/10/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Outubro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 182/2016 - NFS 16837, de 02/12/2015 - Ref. Contrato 04/2012, Serviço de manutenção do Sistema SICS, competência Dezembro/2015.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2016NE01083</t>
+          <t>2016NE01086</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>306.15</v>
+        <v>1020.49</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6764,19 +6764,19 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 100/2016 - NFS 16508, de 10/11/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Novembro/2015</t>
+          <t>Despesas De Exercícios Anteriores - RD 107/2016 - NFS 17305, de 19/01/2016 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Dezembro/2015.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2016NE01108</t>
+          <t>2016NE01104</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>986.48</v>
+        <v>5232.92</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6794,19 +6794,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Reforço - Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de informática para confecção de páginas eletrônicas.</t>
+          <t>Despesas De Exercícios Anteriores - RD 277/2016 - NFS 12881, de 11/12/2014 - Ref. Contrato 11/2011, Serviço eventuais de informática, competência Dezembro/2014.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2016NE01084</t>
+          <t>2016NE01103</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1020.49</v>
+        <v>2035.16</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6824,19 +6824,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 105/2016 - NFS 16208, de 13/10/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Outubro/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 260/2016 - NFS 12236, de 20/10/2014 - Ref. Contrato 11/2011, Serviço de assistência técnica em software.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2016NE01106</t>
+          <t>2016NE01081</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2392.86</v>
+        <v>9895.27</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6854,19 +6854,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ</t>
+          <t>Despesas De Exercícios Anteriores - RD 99/2016 - NFS 14497, de 12/05/2017 - Ref. Contrato 12/2010, Serviço de acesso a rede de internet, competência Maio/2015</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2016NE01111</t>
+          <t>2016NE01109</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>6429.09</v>
+        <v>398.81</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6884,19 +6884,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Referente ao 5º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de informática para confecção de páginas eletrônicas.</t>
+          <t>Despesas De Exercicios Anteriores, RD00117/16, SC00431/16, referente a prestação de serviços de manut. de sistemas de informatica desenvolvido por terceiros - manutenção mensal do sistema SICS - Siste</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2016NE01094</t>
+          <t>2016NE01096</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>398.81</v>
+        <v>1020.49</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6914,19 +6914,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 134/2016 - NFS 14807, de 12/06/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Junho/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 179/2016 - NFS 15335, de 13/08/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Agosto/2015.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2016NE01089</t>
+          <t>2016NE01105</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>398.81</v>
+        <v>5175.24</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6944,19 +6944,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 110/2016 - NFS 16509, de 10/11/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Novembro/2015.</t>
+          <t>Despesas De Exercicios Anteriores, RD00278/16, SC420/16, referente a prestação de serviço de manutenção corretiva e preventiva em equipamentos de automação de escritório no período de novembro/2014, C</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2016NE01101</t>
+          <t>2016NE01095</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>9895.27</v>
+        <v>1020.49</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 257/2016 - NFS 12878, de 11/12/2014 - Ref. Contrato 12/2010, Serviço de acesso a internet -Banda Larga, competência Dezembro/2014.</t>
+          <t>Despesas De Exercícios Anteriores - RD 178/2016 - NFS 15799, de 15/09/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Setembro/2015.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2016NE01097</t>
+          <t>2016NE01098</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7004,19 +7004,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 180/2016 - NFS 15161, de 15/07/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Julho/2015.</t>
+          <t>Despesas De Exercícios Anteriores - RD 181/2016 - NFS 15160, de 15/07/2015 - Ref. Contrato 06/2011, Serviço de hospedagem de site, competência Junho/2015.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2016NE01093</t>
+          <t>2016NE01107</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>398.81</v>
+        <v>3081.37</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Despesas De Exercícios Anteriores - RD 133/2016 - NFS 15096, de 09/07/2015 - Ref. Contrato 04/2012, Serviço de manutenção sistema SICS, competência Julho/2015.</t>
+          <t>Despesas De Exercicios Anteriores, RD00276/16, SC00432/16, Referente a prestação de serviços de manutenção corretiva e preventiva em equipamentos de automação de escritório no período de outubro/14, C</t>
         </is>
       </c>
     </row>
@@ -7071,12 +7071,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025NE0000203</t>
+          <t>2025NE0000204</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7094,19 +7094,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025NE0000204</t>
+          <t>2025NE0000203</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
@@ -7191,12 +7191,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026NE0000006</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>9256</v>
+        <v>2717.66</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7214,19 +7214,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000006</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2717.66</v>
+        <v>9256</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7244,19 +7244,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2015NE00050</t>
+          <t>2015NE00034</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>427.12</v>
+        <v>18780.16</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7274,14 +7274,14 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cobertura 2015</t>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2015NE00059</t>
+          <t>2015NE00060</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7304,19 +7304,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Anulação do Empenho nº 00051/2015 para correção da Referência/Artigo: Art.24; VI; Lei 8.666/93 para Art.24; XVI; Lei 8.666/93.</t>
+          <t>Cobertura financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2015NE00051</t>
+          <t>2015NE00035</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>2040.98</v>
+        <v>10558</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7334,19 +7334,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>3. Termo Aditivo ao Contrato 006/2011-FHAJ, referente a contratação de empresa especializada em serviço de processamento de dados.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2015NE00035</t>
+          <t>2015NE00051</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>10558</v>
+        <v>2040.98</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7364,14 +7364,14 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>3. Termo Aditivo ao Contrato 006/2011-FHAJ, referente a contratação de empresa especializada em serviço de processamento de dados.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2015NE00060</t>
+          <t>2015NE00059</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7394,19 +7394,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015</t>
+          <t>Anulação do Empenho nº 00051/2015 para correção da Referência/Artigo: Art.24; VI; Lei 8.666/93 para Art.24; XVI; Lei 8.666/93.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2015NE00034</t>
+          <t>2015NE00050</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>18780.16</v>
+        <v>427.12</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7424,19 +7424,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+          <t>Cobertura 2015</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2020NE01207</t>
+          <t>2020NE01206</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>15100.2</v>
+        <v>3356.88</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7454,19 +7454,19 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Agosto e setembro/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Agosto e setembro/2020.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2020NE01206</t>
+          <t>2020NE01207</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3356.88</v>
+        <v>15100.2</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7484,19 +7484,19 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: Agosto e setembro/2020.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga - período: Agosto e setembro/2020.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2020NE00819</t>
+          <t>2020NE00820</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>219.52</v>
+        <v>1678.44</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7514,19 +7514,19 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga. Valor complementar ref. às competências janeiro a abril/2020, no valor de R$ 54,88 (mensal).</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: junho/2020.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2020NE00820</t>
+          <t>2020NE00819</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1678.44</v>
+        <v>219.52</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: junho/2020.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 009/17 - Internet banda larga. Valor complementar ref. às competências janeiro a abril/2020, no valor de R$ 54,88 (mensal).</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2015NE00354</t>
+          <t>2015NE00352</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7574,14 +7574,14 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE00060/2015, pelo motivo da fonte de recursos incorreta.</t>
+          <t>Reforço da NE00060/2015, 3º Termo Aditivo ao Contrato nº 006/2011-FHAJ, prestação de serviços de desenvolvimento e confecção e implantação de Web Site.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2015NE00352</t>
+          <t>2015NE00354</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Reforço da NE00060/2015, 3º Termo Aditivo ao Contrato nº 006/2011-FHAJ, prestação de serviços de desenvolvimento e confecção e implantação de Web Site.</t>
+          <t>Anulação parcial da NE00060/2015, pelo motivo da fonte de recursos incorreta.</t>
         </is>
       </c>
     </row>
@@ -7700,12 +7700,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2024NE0000899</t>
+          <t>2024NE0000900</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7723,19 +7723,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2024NE0000900</t>
+          <t>2024NE0000899</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2017NE00668</t>
+          <t>2017NE00669</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.98</v>
+        <v>1020.49</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7779,19 +7779,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Contrato 006/2011 - 6a. TA - Reforço para o mês de Fevereiro e Março/22017 NE 500</t>
+          <t>Contrato 006/2011 - 6.TA - Manutenção site. mês: Abril/2017</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2017NE00666</t>
+          <t>2017NE00667</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>20400</v>
+        <v>1196.43</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7809,19 +7809,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARGA, COM IP DEDICADO, COM VELOCIDADE DE 10 MBPS. (Abril/Maio e Junho)</t>
+          <t>Contratação de pessoa jurídica para prestação de serviço de informática, compreendendo a implantação do SICS - Sistema Inteligente de Controle de Senha para esta fundação. (Maio/junho/julho).</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2017NE00667</t>
+          <t>2017NE00666</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1196.43</v>
+        <v>20400</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7839,14 +7839,14 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Contratação de pessoa jurídica para prestação de serviço de informática, compreendendo a implantação do SICS - Sistema Inteligente de Controle de Senha para esta fundação. (Maio/junho/julho).</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARGA, COM IP DEDICADO, COM VELOCIDADE DE 10 MBPS. (Abril/Maio e Junho)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2017NE00669</t>
+          <t>2017NE00668</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1020.49</v>
+        <v>0.98</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7865,19 +7865,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Contrato 006/2011 - 6.TA - Manutenção site. mês: Abril/2017</t>
+          <t>Contrato 006/2011 - 6a. TA - Reforço para o mês de Fevereiro e Março/22017 NE 500</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025NE0000574</t>
+          <t>2025NE0000573</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7895,19 +7895,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025NE0000573</t>
+          <t>2025NE0000574</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
@@ -7962,21 +7962,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2021NE0000216</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2021NE0000215</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
           <t>03/03/2021</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>6215</v>
+        <v>6199.41</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7985,24 +7981,28 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: 06 a 31 de março/2021.</t>
+          <t>ANULAÇÃO DA NE 213/2021 POR VALOR INCORRETO.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2021NE0000215</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>2021NE0000216</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
           <t>03/03/2021</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>6199.41</v>
+        <v>6215</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 213/2021 POR VALOR INCORRETO.</t>
+          <t>4º TA ao CT 009/2017, contratação de empresa especializada para prestação de serviços de acesso à internet Banda Larga com IP dedicado, com velocidade de 35 Mbps. Período: 06 a 31 de março/2021.</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8078,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2022NE0000022</t>
+          <t>2022NE0000034</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6473.1</v>
+        <v>16158.28</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8101,19 +8101,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo); Período: Janeiro a março/2022.</t>
+          <t>Referente ao 4º TA ao CT 009/2017-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado; Período: Janeiro, fevereiro e de 01 a 05 de março/2022.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2022NE0000034</t>
+          <t>2022NE0000022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>16158.28</v>
+        <v>6473.1</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA ao CT 009/2017-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado; Período: Janeiro, fevereiro e de 01 a 05 de março/2022.</t>
+          <t>Referente ao 4º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo); Período: Janeiro a março/2022.</t>
         </is>
       </c>
     </row>
@@ -8198,12 +8198,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025NE0000004</t>
+          <t>2025NE0000012</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>9256.1</v>
+        <v>2717.66</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8221,19 +8221,19 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
+          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025NE0000012</t>
+          <t>2025NE0000004</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>2717.66</v>
+        <v>9256.1</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8251,19 +8251,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃODE EMPRESA ESPECIALIZADA PARA O SERVIÇO DE CONFECÇÃO, DESENVOLVIMENTO E HOSPEDAGEM DE PÁGINA ELETRÔNICA E SITE INSTITUCIONAL PARA ATENDER A NECESSIDADES DA FUNDAÇÃO HOSPITAL ADRIANO JORGE –</t>
+          <t>Contratação de Empresa Especializada em serviços de acesso à Internet Banda Larga, com IP Dedicado, com Velocidade de 37Mbps, para atender à necessidades desta FHAJ, com reajuste em 23% para realinham</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000006</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>2297.09</v>
+        <v>7525.43</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8281,19 +8281,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Referente ao 5º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Janeiro/2023.</t>
+          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Janeiro/2023.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>7525.43</v>
+        <v>2297.09</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8311,19 +8311,19 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Referente ao CT 008/2022-FHAJ, serviços de acesso à Internet banda larga, com Ip dedicado. Período: Janeiro/2023.</t>
+          <t>Referente ao 5º TA ao CT 001/2018-FHAJ, serviços de disponibilidade de gestor de conteúdo WEB (Publicações padrão Governo). Período: Janeiro/2023.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2020NE00004</t>
+          <t>2020NE00008</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>22376.7</v>
+        <v>4870.68</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8341,19 +8341,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Referente ao 2º TA ao CT nº 009/17 - internet banda larga - Período: jan a mar/2020.</t>
+          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: jan, fev e parcial de mar/2020.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2020NE00008</t>
+          <t>2020NE00004</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>4870.68</v>
+        <v>22376.7</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8371,19 +8371,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas. Período: jan, fev e parcial de mar/2020.</t>
+          <t>Referente ao 2º TA ao CT nº 009/17 - internet banda larga - Período: jan a mar/2020.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2019NE00013</t>
+          <t>2019NE00024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>16400</v>
+        <v>4425.87</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8401,19 +8401,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>01 TA ao CT 009/17 - serviços de Internet banda larga.</t>
+          <t>1º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2019NE00024</t>
+          <t>2019NE00013</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4425.87</v>
+        <v>16400</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8431,19 +8431,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>1º TA ao CT nº 001/2018-FHAJ de serviço de confecção de páginas eletrônicas.</t>
+          <t>01 TA ao CT 009/17 - serviços de Internet banda larga.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2018NE00031</t>
+          <t>2018NE00055</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1020.49</v>
+        <v>6800</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8461,19 +8461,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>DEAS - Serviço de Hospedagem do site ref. CT 06/11, competência Agosto/17 conforme NFS 24368, de 15/08/2018. SC 020/2018, RD 116/2018.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARGA, COM IP DEDICADO, COM VELOCIDADE DE 10 MBPS. TERMO DE CONTRATO 009/2017-FHAJ</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2018NE00063</t>
+          <t>2018NE00048</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1475.29</v>
+        <v>398.81</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB - CT 001/2018</t>
+          <t>DEAS - Serviço de Senhas - SCI no mês Outubr2018.</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2018NE00048</t>
+          <t>2018NE00063</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>398.81</v>
+        <v>1475.29</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8551,19 +8551,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>DEAS - Serviço de Senhas - SCI no mês Outubr2018.</t>
+          <t>SERVIÇO DE DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB - CT 001/2018</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2018NE00055</t>
+          <t>2018NE00031</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>6800</v>
+        <v>1020.49</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8581,19 +8581,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARGA, COM IP DEDICADO, COM VELOCIDADE DE 10 MBPS. TERMO DE CONTRATO 009/2017-FHAJ</t>
+          <t>DEAS - Serviço de Hospedagem do site ref. CT 06/11, competência Agosto/17 conforme NFS 24368, de 15/08/2018. SC 020/2018, RD 116/2018.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2017NE00084</t>
+          <t>2017NE00083</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>398.81</v>
+        <v>1020.49</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8611,19 +8611,19 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>4. Termo aditivo ao Contrato 004/2012-FHAJ - Serviço de Senhas</t>
+          <t>Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de desenvolvimento, confecção e implantação de Web Site.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2017NE00083</t>
+          <t>2017NE00084</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1020.49</v>
+        <v>398.81</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8641,19 +8641,19 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Referente ao 6º Termo Aditivo ao Contrato nº 006/2011-FHAJ, serviços de desenvolvimento, confecção e implantação de Web Site.</t>
+          <t>4. Termo aditivo ao Contrato 004/2012-FHAJ - Serviço de Senhas</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2014NE00047</t>
+          <t>2014NE00053</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>405.24</v>
+        <v>47263.4</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8671,19 +8671,19 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2012 - Manutenção Sist Senhas- SICS</t>
+          <t>Contrato No. 12/2010 - Internet/Computador banda 3.256Kb-MetroMAO</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2014NE00073</t>
+          <t>2014NE00058</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>11/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>35211.47</v>
+        <v>3873.56</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8701,19 +8701,19 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Contrato No. 11/2011 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 6/2011 - Desenvolvimento e Hospedagem de Site</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2014NE00058</t>
+          <t>2014NE00073</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>11/2011</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>3873.56</v>
+        <v>35211.47</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8731,19 +8731,19 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Contrato No. 6/2011 - Desenvolvimento e Hospedagem de Site</t>
+          <t>Contrato No. 11/2011 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2014NE00053</t>
+          <t>2014NE00047</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>47263.4</v>
+        <v>405.24</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8761,24 +8761,28 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Contrato No. 12/2010 - Internet/Computador banda 3.256Kb-MetroMAO</t>
+          <t>Contrato No. 4/2012 - Manutenção Sist Senhas- SICS</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2017NE00817</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
+          <t>2017NE00816</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>398.81</v>
+        <v>1020.49</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8787,28 +8791,24 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Contratação de pessoa jurídica para prestação de serviço de informática, compreendendo a implantação do SICS - Sistema Inteligente de Controle de Senha para esta fundação.</t>
+          <t>Para atender despesa com Contrato de serviço de informática.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2017NE00816</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>6/2011</t>
-        </is>
-      </c>
+          <t>2017NE00817</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1020.49</v>
+        <v>398.81</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Para atender despesa com Contrato de serviço de informática.</t>
+          <t>Contratação de pessoa jurídica para prestação de serviço de informática, compreendendo a implantação do SICS - Sistema Inteligente de Controle de Senha para esta fundação.</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2016NE00698</t>
+          <t>2016NE00679</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ</t>
+          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ.</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2016NE00679</t>
+          <t>2016NE00698</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8937,19 +8937,19 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ.</t>
+          <t>Reforço a NE00200/2016, referente ao 4º Termo Aditivo ao Contrato nº 004/2012-FHAJ</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2015NE00567</t>
+          <t>2015NE00569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>12/2010</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>398.81</v>
+        <v>9390.08</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>cobertura maio/2015</t>
+          <t>Reforço a NE00034/2015, 4º Termo Aditivo ao Contrato nº 12/2010-FHAJ, referente a serviços de acesso a Internet.</t>
         </is>
       </c>
     </row>
@@ -9004,12 +9004,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2015NE00569</t>
+          <t>2015NE00567</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>12/2010</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>9390.08</v>
+        <v>398.81</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Reforço a NE00034/2015, 4º Termo Aditivo ao Contrato nº 12/2010-FHAJ, referente a serviços de acesso a Internet.</t>
+          <t>cobertura maio/2015</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2015NE00206</t>
+          <t>2015NE00200</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9108,7 +9108,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1020.49</v>
+        <v>398.81</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9117,19 +9117,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>cobertura março 2015</t>
+          <t>COBERTURA MARÇO 2015</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2015NE00200</t>
+          <t>2015NE00206</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9138,7 +9138,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>398.81</v>
+        <v>1020.49</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9147,24 +9147,28 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>COBERTURA MARÇO 2015</t>
+          <t>cobertura março 2015</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2019NE00173</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr"/>
+          <t>2019NE00176</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr">
         <is>
           <t>01/03/2019</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1666.67</v>
+        <v>5221.86</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9173,17 +9177,21 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE00013, pelo motivo do empenhamento a maior no mês de março/2019.</t>
+          <t>Referente ao 2º TA ao CT nº 009/17 - internet banda larga - parcial de março/2019.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2019NE00178</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
+          <t>2019NE00177</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr">
         <is>
           <t>01/03/2019</t>
@@ -9199,21 +9207,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE00024/2019, pelo motivo da descrição incorreta.</t>
+          <t>Referente ao 1º AD ao CT nº 001/2018-FHAJ, serv. de confecções de páginas eletrônicas (reforço à NE24/2019 - complemento de março/19).</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2019NE00177</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2019NE00178</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
           <t>01/03/2019</t>
@@ -9229,28 +9233,24 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Referente ao 1º AD ao CT nº 001/2018-FHAJ, serv. de confecções de páginas eletrônicas (reforço à NE24/2019 - complemento de março/19).</t>
+          <t>Anulação parcial da NE00024/2019, pelo motivo da descrição incorreta.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2019NE00176</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2019NE00173</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
           <t>01/03/2019</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>5221.86</v>
+        <v>1666.67</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Referente ao 2º TA ao CT nº 009/17 - internet banda larga - parcial de março/2019.</t>
+          <t>Anulação parcial da NE00013, pelo motivo do empenhamento a maior no mês de março/2019.</t>
         </is>
       </c>
     </row>
@@ -9296,12 +9296,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2016NE00074</t>
+          <t>2016NE00075</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>2040.98</v>
+        <v>427.12</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9319,19 +9319,19 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>5º Termo Aditivo ao Contrato nº 006/2011-FHAJ, de prestação de serviços para desenvolvimento, confecção de páginas eletrônicas e hospedagem de Site Institucional desta Fundação.</t>
+          <t>Referente ao 3º Termo Aditivo ao Contrato nº 004/2012-FHAJ, para prestação de serviços de informática, instalação, implantação, manutenção do Sistema Inteligente de Senhas-SICS.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2016NE00075</t>
+          <t>2016NE00074</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>427.12</v>
+        <v>2040.98</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Referente ao 3º Termo Aditivo ao Contrato nº 004/2012-FHAJ, para prestação de serviços de informática, instalação, implantação, manutenção do Sistema Inteligente de Senhas-SICS.</t>
+          <t>5º Termo Aditivo ao Contrato nº 006/2011-FHAJ, de prestação de serviços para desenvolvimento, confecção de páginas eletrônicas e hospedagem de Site Institucional desta Fundação.</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/FHAJ/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FHAJ/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-07-31</t>
         </is>
       </c>
     </row>
